--- a/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,142 +99,142 @@
     <t>Kind</t>
   </si>
   <si>
-    <t>resource</t>
+    <t>logical</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Base Definition</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Element</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Derivation</t>
+  </si>
+  <si>
+    <t>specialization</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Slice Name</t>
+  </si>
+  <si>
+    <t>Alias(s)</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Must Support?</t>
+  </si>
+  <si>
+    <t>Is Modifier?</t>
+  </si>
+  <si>
+    <t>Is Summary?</t>
+  </si>
+  <si>
+    <t>Type(s)</t>
+  </si>
+  <si>
+    <t>Short</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>Meaning When Missing</t>
+  </si>
+  <si>
+    <t>Fixed Value</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Minimum Value</t>
+  </si>
+  <si>
+    <t>Maximum Value</t>
+  </si>
+  <si>
+    <t>Maximum Length</t>
+  </si>
+  <si>
+    <t>Binding Strength</t>
+  </si>
+  <si>
+    <t>Binding Description</t>
+  </si>
+  <si>
+    <t>Binding Value Set</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Slicing Discriminator</t>
+  </si>
+  <si>
+    <t>Slicing Description</t>
+  </si>
+  <si>
+    <t>Slicing Ordered</t>
+  </si>
+  <si>
+    <t>Slicing Rules</t>
+  </si>
+  <si>
+    <t>Base Path</t>
+  </si>
+  <si>
+    <t>Base Min</t>
+  </si>
+  <si>
+    <t>Base Max</t>
+  </si>
+  <si>
+    <t>Condition(s)</t>
+  </si>
+  <si>
+    <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: RIM Mapping</t>
+  </si>
+  <si>
     <t>schedule-supporting-data</t>
-  </si>
-  <si>
-    <t>Base Definition</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Element</t>
-  </si>
-  <si>
-    <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Derivation</t>
-  </si>
-  <si>
-    <t>specialization</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Slice Name</t>
-  </si>
-  <si>
-    <t>Alias(s)</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Must Support?</t>
-  </si>
-  <si>
-    <t>Is Modifier?</t>
-  </si>
-  <si>
-    <t>Is Summary?</t>
-  </si>
-  <si>
-    <t>Type(s)</t>
-  </si>
-  <si>
-    <t>Short</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Requirements</t>
-  </si>
-  <si>
-    <t>Default Value</t>
-  </si>
-  <si>
-    <t>Meaning When Missing</t>
-  </si>
-  <si>
-    <t>Fixed Value</t>
-  </si>
-  <si>
-    <t>Pattern</t>
-  </si>
-  <si>
-    <t>Example</t>
-  </si>
-  <si>
-    <t>Minimum Value</t>
-  </si>
-  <si>
-    <t>Maximum Value</t>
-  </si>
-  <si>
-    <t>Maximum Length</t>
-  </si>
-  <si>
-    <t>Binding Strength</t>
-  </si>
-  <si>
-    <t>Binding Description</t>
-  </si>
-  <si>
-    <t>Binding Value Set</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Slicing Discriminator</t>
-  </si>
-  <si>
-    <t>Slicing Description</t>
-  </si>
-  <si>
-    <t>Slicing Ordered</t>
-  </si>
-  <si>
-    <t>Slicing Rules</t>
-  </si>
-  <si>
-    <t>Base Path</t>
-  </si>
-  <si>
-    <t>Base Min</t>
-  </si>
-  <si>
-    <t>Base Max</t>
-  </si>
-  <si>
-    <t>Condition(s)</t>
-  </si>
-  <si>
-    <t>Constraint(s)</t>
-  </si>
-  <si>
-    <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>0</t>
@@ -892,31 +892,31 @@
         <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -969,123 +969,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>36</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>37</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>72</v>
-      </c>
-      <c r="AK1" t="s" s="1">
-        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">

--- a/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
+++ b/jaspr/web/cicada_ig/StructureDefinition-schedule-supporting-data.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
